--- a/design_tables/excel/CardTypeConfig.xlsx
+++ b/design_tables/excel/CardTypeConfig.xlsx
@@ -85,17 +85,6 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CardTypeConfigTable" displayName="CardTypeConfigTable" ref="A1:C10" headerRowCount="1">
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="id"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -364,8 +353,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4124b4fcd695414b"/>
-  </x:tableParts>
 </x:worksheet>
 </file>